--- a/feedback_surveys/022_employee_experience_feedback_form--feedback_surveys.xlsx
+++ b/feedback_surveys/022_employee_experience_feedback_form--feedback_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -780,8 +780,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
-    <col width="44" customWidth="1" min="2" max="2"/>
-    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -809,12 +809,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'never'}</t>
+          <t>never</t>
         </is>
       </c>
     </row>
@@ -826,12 +826,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'occasionally'}</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'occasionally'}</t>
+          <t>occasionally</t>
         </is>
       </c>
     </row>
@@ -860,12 +860,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'regularly'}</t>
+          <t>regularly</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'regularly'}</t>
+          <t>regularly</t>
         </is>
       </c>
     </row>
@@ -877,12 +877,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
     </row>
@@ -894,12 +894,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'too_often'}</t>
+          <t>too_often</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'too_often'}</t>
+          <t>too often</t>
         </is>
       </c>
     </row>
@@ -911,12 +911,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'just_right'}</t>
+          <t>just_right</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'just_right'}</t>
+          <t>just right</t>
         </is>
       </c>
     </row>
@@ -928,12 +928,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'too_seldom'}</t>
+          <t>too_seldom</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'too_seldom'}</t>
+          <t>too seldom</t>
         </is>
       </c>
     </row>
@@ -945,12 +945,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'supportive'}</t>
+          <t>supportive</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'supportive'}</t>
+          <t>supportive</t>
         </is>
       </c>
     </row>
@@ -962,12 +962,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'helpful'}</t>
+          <t>helpful</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'helpful'}</t>
+          <t>helpful</t>
         </is>
       </c>
     </row>
@@ -979,12 +979,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'distant'}</t>
+          <t>distant</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'distant'}</t>
+          <t>distant</t>
         </is>
       </c>
     </row>
@@ -996,12 +996,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'micromanaging'}</t>
+          <t>micromanaging</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'micromanaging'}</t>
+          <t>micromanaging</t>
         </is>
       </c>
     </row>
@@ -1013,12 +1013,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'unhelpful'}</t>
+          <t>unhelpful</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'unhelpful'}</t>
+          <t>unhelpful</t>
         </is>
       </c>
     </row>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'very_satisfied'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'very_satisfied'}</t>
+          <t>very satisfied</t>
         </is>
       </c>
     </row>
@@ -1047,12 +1047,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'somewhat_satisfied'}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'somewhat_satisfied'}</t>
+          <t>somewhat satisfied</t>
         </is>
       </c>
     </row>
@@ -1064,12 +1064,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -1081,12 +1081,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'somewhat_dissatisfied'}</t>
+          <t>somewhat_dissatisfied</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'somewhat_dissatisfied'}</t>
+          <t>somewhat dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1098,12 +1098,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'very_dissatisfied'}</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'very_dissatisfied'}</t>
+          <t>very dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1115,12 +1115,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'very_satisfied'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'very_satisfied'}</t>
+          <t>very satisfied</t>
         </is>
       </c>
     </row>
@@ -1132,12 +1132,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'somewhat_satisfied'}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'somewhat_satisfied'}</t>
+          <t>somewhat satisfied</t>
         </is>
       </c>
     </row>
@@ -1149,12 +1149,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -1166,12 +1166,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'somewhat_dissatisfied'}</t>
+          <t>somewhat_dissatisfied</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'somewhat_dissatisfied'}</t>
+          <t>somewhat dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'very_dissatisfied'}</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'very_dissatisfied'}</t>
+          <t>very dissatisfied</t>
         </is>
       </c>
     </row>
